--- a/other/vacuum_instrumentation_bundle_v2/bom/BOM_switch_panel_test_9-27-2026.xlsx
+++ b/other/vacuum_instrumentation_bundle_v2/bom/BOM_switch_panel_test_9-27-2026.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aiden\Documents\GitHub\coldex-instrumentation\other\vacuum_instrumentation_bundle_v2\bom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ABADE07-1FC3-4834-8B05-9F005E73176F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80173FE0-B5D2-4685-83A0-E94332BA362F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21240" xr2:uid="{BD5EB8A6-8342-49EB-8243-34465C06A882}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>Unit</t>
   </si>
@@ -31,16 +44,37 @@
     <t>Manufacturer / Part</t>
   </si>
   <si>
-    <t>Use</t>
-  </si>
-  <si>
     <t>Purchase URL</t>
   </si>
   <si>
+    <t>ea</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
     <t>~Unit Price</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/mts-202-125VAC-Position-Toggle-Switch/dp/B0799JV8GN/ref=sr_1_3?channelId=500&amp;clpRedir=Y&amp;dib=eyJ2IjoiMSJ9.-NHYFqEB89nrAFkIqvFPx70RwLQbMEt-OOqiJhT-_Vx1KSQc875kSTl2A93RGoRTyvkpCROvvLIiiPgXvS2g4rmIuf1QaSY__mNSk5D_F8I9uzOOUzJBdsz5bRlsnZe8uAevVagICzZnKKmpdoPv6i5XSol-PjvmJ8oIYoGgPlgi9JanQGFPvxHtTOkUPl-GpYI9m-k_q1sVcJ3aANYNKfKKGzec9_mhKadyaMZHgI4.I_wSMllDmaD5Gqk7rvWTTBPrHWCMRAeHKw64_JJkV4c&amp;dib_tag=se&amp;keywords=DPDT%2BSwitch&amp;plpRedirect=mhFallback&amp;qid=1790540410&amp;sr=8-3&amp;th=1</t>
+  </si>
+  <si>
+    <t>Taiss 10pcs DPDT Mini Toggle Switch - 6-Pin 3 Position ON/Off/ON - 6A 125V MTS-203</t>
+  </si>
+  <si>
+    <t>Taiss</t>
+  </si>
+  <si>
+    <t>https://www.amazon.com/BOJACK-Values-Resistor-Resistors-Assortment/dp/B08FD1XVL6/ref=sr_1_1?crid=2YDDZR84FFBX1&amp;dib=eyJ2IjoiMSJ9.QqtzmCG7CKt6OW1fHgTb26uI1Fk5beBArSayNzxiB8TE15Dl929e_fxCSf_UOTxzfJS6ONIcmTQgz_zJDgaDfFKuCJoZ1Guz9H3uyeQUvzaQhnJF7xg5SA1hH8ZKyVGBYCt74IvCzfDrO4sqjYkVh8ZIJw2N3-BuXq1MZii-4Xkybh4OsZzZD99ooNJQOy9S2xX_Ed9wMPhE6w_eFY2TNKjeOmlPqd7X50kNWdJ2gNE.ETPAMNryD9mquSsqGZudTlVrB2OSgKTJif7BOA5WqVM&amp;dib_tag=se&amp;keywords=resistor%2Bkit&amp;qid=1790541502&amp;sprefix=resistor%2Bki%2Caps%2C221&amp;sr=8-1&amp;th=1</t>
+  </si>
+  <si>
+    <t>BOJACK 1000 Pcs 25 Values Resistor Kit 1 Ohm-1M Ohm with 5% 1/4W Carbon Film Resistors Assortment</t>
+  </si>
+  <si>
+    <t>BOJACK</t>
+  </si>
+  <si>
+    <t>Total</t>
   </si>
 </sst>
 </file>
@@ -533,21 +567,8 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="fill"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
-      <alignment horizontal="fill"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -555,7 +576,19 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="fill"/>
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="fill" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42" applyAlignment="1">
+      <alignment horizontal="fill" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="fill" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -933,144 +966,110 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1332F0E5-D3FB-47C8-B637-9994B3D9B4BC}">
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="48.42578125" style="1" customWidth="1"/>
-    <col min="4" max="4" width="27.7109375" customWidth="1"/>
-    <col min="5" max="5" width="11" customWidth="1"/>
-    <col min="6" max="6" width="53.7109375" style="6" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" style="2" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="1"/>
+    <col min="2" max="2" width="12.42578125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="48.42578125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="11" style="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="C2" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="1">
+        <v>8.66</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D2" s="6"/>
+    <row r="3" spans="1:6" ht="45" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>1</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="1">
+        <v>9.99</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D3" s="6"/>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F5" s="6"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D4" s="6"/>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F6" s="6"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D5" s="6"/>
-      <c r="G5" s="3"/>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F7" s="6"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D6" s="6"/>
-      <c r="G6" s="3"/>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D7" s="6"/>
-      <c r="G7" s="3"/>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" s="1">
+        <f>SUMPRODUCT(A2:A3,E2:E3)</f>
+        <v>18.649999999999999</v>
+      </c>
+      <c r="F11" s="6"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D8" s="6"/>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F16" s="6"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D9" s="6"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D10" s="6"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D11" s="6"/>
-      <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D12" s="6"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D13" s="6"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D14" s="6"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D15" s="6"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D16" s="6"/>
-      <c r="G16" s="3"/>
-    </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D17" s="6"/>
-    </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D18" s="6"/>
-      <c r="G18" s="3"/>
-    </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D19" s="6"/>
-    </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D20" s="6"/>
-    </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D21" s="6"/>
-    </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D22" s="6"/>
-    </row>
-    <row r="23" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D23" s="6"/>
-    </row>
-    <row r="24" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D24" s="6"/>
-    </row>
-    <row r="25" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D25" s="6"/>
-    </row>
-    <row r="26" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D26" s="6"/>
-    </row>
-    <row r="27" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D27" s="6"/>
-    </row>
-    <row r="28" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D28" s="6"/>
-    </row>
-    <row r="29" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D29" s="6"/>
-    </row>
-    <row r="30" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D30" s="6"/>
-    </row>
-    <row r="31" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D31" s="6"/>
-    </row>
-    <row r="32" spans="4:7" x14ac:dyDescent="0.25">
-      <c r="D32" s="6"/>
-    </row>
-    <row r="33" spans="4:4" x14ac:dyDescent="0.25">
-      <c r="D33" s="6"/>
+    <row r="18" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F18" s="6"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" display="https://www.amazon.com/mts-202-125VAC-Position-Toggle-Switch/dp/B0799JV8GN/ref=sr_1_3?channelId=500&amp;clpRedir=Y&amp;dib=eyJ2IjoiMSJ9.-NHYFqEB89nrAFkIqvFPx70RwLQbMEt-OOqiJhT-_Vx1KSQc875kSTl2A93RGoRTyvkpCROvvLIiiPgXvS2g4rmIuf1QaSY__mNSk5D_F8I9uzOOUzJBdsz5bRlsnZe8uAevVagICzZnKKmpdoPv6i5XSol-PjvmJ8oIYoGgPlgi9JanQGFPvxHtTOkUPl-GpYI9m-k_q1sVcJ3aANYNKfKKGzec9_mhKadyaMZHgI4.I_wSMllDmaD5Gqk7rvWTTBPrHWCMRAeHKw64_JJkV4c&amp;dib_tag=se&amp;keywords=DPDT%2BSwitch&amp;plpRedirect=mhFallback&amp;qid=1790540410&amp;sr=8-3&amp;th=1" xr:uid="{A7FDB01F-6683-4868-A139-93E3495CEA98}"/>
+    <hyperlink ref="F3" r:id="rId2" display="https://www.amazon.com/BOJACK-Values-Resistor-Resistors-Assortment/dp/B08FD1XVL6/ref=sr_1_1?crid=2YDDZR84FFBX1&amp;dib=eyJ2IjoiMSJ9.QqtzmCG7CKt6OW1fHgTb26uI1Fk5beBArSayNzxiB8TE15Dl929e_fxCSf_UOTxzfJS6ONIcmTQgz_zJDgaDfFKuCJoZ1Guz9H3uyeQUvzaQhnJF7xg5SA1hH8ZKyVGBYCt74IvCzfDrO4sqjYkVh8ZIJw2N3-BuXq1MZii-4Xkybh4OsZzZD99ooNJQOy9S2xX_Ed9wMPhE6w_eFY2TNKjeOmlPqd7X50kNWdJ2gNE.ETPAMNryD9mquSsqGZudTlVrB2OSgKTJif7BOA5WqVM&amp;dib_tag=se&amp;keywords=resistor%2Bkit&amp;qid=1790541502&amp;sprefix=resistor%2Bki%2Caps%2C221&amp;sr=8-1&amp;th=1" xr:uid="{1E2498E2-715F-4C33-A536-F1D30011EA11}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId3"/>
 </worksheet>
 </file>